--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4132B0D-F834-4B1F-8FCA-115C90A3D196}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A48BDAE-6876-4B45-89E4-7280EC32E292}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$312</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="347">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1073,6 +1073,12 @@
   </si>
   <si>
     <t>COAG-REC</t>
+  </si>
+  <si>
+    <t>COAG-BHZ</t>
+  </si>
+  <si>
+    <t>CCIM</t>
   </si>
 </sst>
 </file>
@@ -7264,7 +7270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:E310"/>
+  <dimension ref="A1:E312"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -7979,7 +7985,7 @@
         <v>326</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -7987,7 +7993,7 @@
         <v>326</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -7995,15 +8001,15 @@
         <v>326</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>326</v>
+      <c r="B85" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -8011,7 +8017,7 @@
         <v>326</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>2</v>
+        <v>326</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -8019,7 +8025,7 @@
         <v>326</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>104</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -8027,7 +8033,7 @@
         <v>326</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -8035,7 +8041,7 @@
         <v>326</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -8043,7 +8049,7 @@
         <v>326</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -8051,7 +8057,7 @@
         <v>326</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -8059,7 +8065,7 @@
         <v>326</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -8067,7 +8073,7 @@
         <v>326</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -8075,7 +8081,7 @@
         <v>326</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -8083,7 +8089,7 @@
         <v>326</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -8091,7 +8097,7 @@
         <v>326</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -8099,7 +8105,7 @@
         <v>326</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -8107,7 +8113,7 @@
         <v>326</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -8115,7 +8121,7 @@
         <v>326</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -8123,7 +8129,7 @@
         <v>326</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -8131,7 +8137,7 @@
         <v>326</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -8139,7 +8145,7 @@
         <v>326</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -8147,7 +8153,7 @@
         <v>326</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -8155,7 +8161,7 @@
         <v>326</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -8163,7 +8169,7 @@
         <v>326</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -8171,7 +8177,7 @@
         <v>326</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -8179,7 +8185,7 @@
         <v>326</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -8187,7 +8193,7 @@
         <v>326</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
@@ -8195,7 +8201,7 @@
         <v>326</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -8203,7 +8209,7 @@
         <v>326</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -8211,7 +8217,7 @@
         <v>326</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -8219,7 +8225,7 @@
         <v>326</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -8227,7 +8233,7 @@
         <v>326</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -8235,7 +8241,7 @@
         <v>326</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -8243,7 +8249,7 @@
         <v>326</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -8251,7 +8257,7 @@
         <v>326</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -8259,7 +8265,7 @@
         <v>326</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -8267,7 +8273,7 @@
         <v>326</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -8275,15 +8281,15 @@
         <v>326</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -8291,7 +8297,7 @@
         <v>301</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -8299,7 +8305,7 @@
         <v>301</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -8307,7 +8313,7 @@
         <v>301</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -8315,7 +8321,7 @@
         <v>301</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -8323,7 +8329,7 @@
         <v>301</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -8331,7 +8337,7 @@
         <v>301</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -8339,7 +8345,7 @@
         <v>301</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -8347,7 +8353,7 @@
         <v>301</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -8355,7 +8361,7 @@
         <v>301</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -8363,7 +8369,7 @@
         <v>301</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -8371,7 +8377,7 @@
         <v>301</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -8379,7 +8385,7 @@
         <v>301</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -8387,7 +8393,7 @@
         <v>301</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -8395,7 +8401,7 @@
         <v>301</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -8403,7 +8409,7 @@
         <v>301</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -8411,7 +8417,7 @@
         <v>301</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -8419,7 +8425,7 @@
         <v>301</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -8427,15 +8433,15 @@
         <v>301</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>170</v>
+        <v>301</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -8443,7 +8449,7 @@
         <v>308</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -8451,7 +8457,7 @@
         <v>308</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -8459,7 +8465,7 @@
         <v>308</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -8467,7 +8473,7 @@
         <v>308</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -8475,7 +8481,7 @@
         <v>308</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -8483,7 +8489,7 @@
         <v>308</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -8491,7 +8497,7 @@
         <v>308</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -8499,15 +8505,15 @@
         <v>308</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>4</v>
+        <v>308</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -8515,7 +8521,7 @@
         <v>309</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -8523,7 +8529,7 @@
         <v>309</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -8531,7 +8537,7 @@
         <v>309</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -8539,7 +8545,7 @@
         <v>309</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -8547,7 +8553,7 @@
         <v>309</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -8555,7 +8561,7 @@
         <v>309</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -8563,7 +8569,7 @@
         <v>309</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -8571,7 +8577,7 @@
         <v>309</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -8579,7 +8585,7 @@
         <v>309</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -8587,7 +8593,7 @@
         <v>309</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -8595,7 +8601,7 @@
         <v>309</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -8603,7 +8609,7 @@
         <v>309</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -8611,7 +8617,7 @@
         <v>309</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -8619,7 +8625,7 @@
         <v>309</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -8627,7 +8633,7 @@
         <v>309</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -8635,7 +8641,7 @@
         <v>309</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -8643,7 +8649,7 @@
         <v>309</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -8651,7 +8657,7 @@
         <v>309</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -8659,7 +8665,7 @@
         <v>309</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -8667,7 +8673,7 @@
         <v>309</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -8675,7 +8681,7 @@
         <v>309</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -8683,7 +8689,7 @@
         <v>309</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -8691,7 +8697,7 @@
         <v>309</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -8699,7 +8705,7 @@
         <v>309</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -8707,7 +8713,7 @@
         <v>309</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -8715,7 +8721,7 @@
         <v>309</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -8723,7 +8729,7 @@
         <v>309</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -8731,23 +8737,23 @@
         <v>309</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>33</v>
+        <v>309</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B178" s="5" t="s">
-        <v>335</v>
+      <c r="B178" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -8755,7 +8761,7 @@
         <v>310</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -8763,7 +8769,7 @@
         <v>310</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -8771,15 +8777,15 @@
         <v>310</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>62</v>
+      <c r="B182" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -8787,7 +8793,7 @@
         <v>310</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -8795,7 +8801,7 @@
         <v>310</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -8803,7 +8809,7 @@
         <v>310</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -8811,7 +8817,7 @@
         <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -8819,7 +8825,7 @@
         <v>310</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -8827,7 +8833,7 @@
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -8835,7 +8841,7 @@
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -8843,7 +8849,7 @@
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -8851,7 +8857,7 @@
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -8859,7 +8865,7 @@
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -8867,7 +8873,7 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -8875,7 +8881,7 @@
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -8883,7 +8889,7 @@
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -8891,7 +8897,7 @@
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -8899,7 +8905,7 @@
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -8907,7 +8913,7 @@
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -8915,7 +8921,7 @@
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -8923,7 +8929,7 @@
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -8931,7 +8937,7 @@
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -8939,7 +8945,7 @@
         <v>310</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -8947,7 +8953,7 @@
         <v>310</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -8955,7 +8961,7 @@
         <v>310</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -8963,7 +8969,7 @@
         <v>310</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -8971,7 +8977,7 @@
         <v>310</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -8979,7 +8985,7 @@
         <v>310</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -8987,7 +8993,7 @@
         <v>310</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -8995,7 +9001,7 @@
         <v>310</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -9003,7 +9009,7 @@
         <v>310</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -9011,7 +9017,7 @@
         <v>310</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -9019,15 +9025,15 @@
         <v>310</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -9035,7 +9041,7 @@
         <v>313</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -9043,7 +9049,7 @@
         <v>313</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -9051,7 +9057,7 @@
         <v>313</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -9059,7 +9065,7 @@
         <v>313</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -9067,7 +9073,7 @@
         <v>313</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -9075,7 +9081,7 @@
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -9083,7 +9089,7 @@
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>52</v>
+        <v>346</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -9091,7 +9097,7 @@
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -9099,7 +9105,7 @@
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -9107,7 +9113,7 @@
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -9115,7 +9121,7 @@
         <v>313</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -9123,7 +9129,7 @@
         <v>313</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -9131,7 +9137,7 @@
         <v>313</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -9139,7 +9145,7 @@
         <v>313</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -9147,7 +9153,7 @@
         <v>313</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -9155,7 +9161,7 @@
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -9163,7 +9169,7 @@
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -9171,7 +9177,7 @@
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -9179,7 +9185,7 @@
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -9187,7 +9193,7 @@
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -9195,7 +9201,7 @@
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -9203,7 +9209,7 @@
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -9211,7 +9217,7 @@
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -9219,7 +9225,7 @@
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -9227,7 +9233,7 @@
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -9235,7 +9241,7 @@
         <v>313</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -9243,7 +9249,7 @@
         <v>313</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -9251,7 +9257,7 @@
         <v>313</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -9259,7 +9265,7 @@
         <v>313</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -9267,7 +9273,7 @@
         <v>313</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -9275,7 +9281,7 @@
         <v>313</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -9283,7 +9289,7 @@
         <v>313</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -9291,7 +9297,7 @@
         <v>313</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -9299,7 +9305,7 @@
         <v>313</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -9307,7 +9313,7 @@
         <v>313</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>303</v>
+        <v>230</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -9315,23 +9321,23 @@
         <v>313</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>313</v>
+        <v>241</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>21</v>
+        <v>303</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>44</v>
+        <v>313</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -9339,7 +9345,7 @@
         <v>314</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -9347,7 +9353,7 @@
         <v>314</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -9355,7 +9361,7 @@
         <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -9363,7 +9369,7 @@
         <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -9371,7 +9377,7 @@
         <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -9379,7 +9385,7 @@
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -9387,7 +9393,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -9395,7 +9401,7 @@
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -9403,7 +9409,7 @@
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -9411,7 +9417,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -9419,7 +9425,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -9427,7 +9433,7 @@
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -9435,7 +9441,7 @@
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -9443,7 +9449,7 @@
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -9451,7 +9457,7 @@
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -9459,7 +9465,7 @@
         <v>314</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -9467,7 +9473,7 @@
         <v>314</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -9475,7 +9481,7 @@
         <v>314</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -9483,7 +9489,7 @@
         <v>314</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -9491,7 +9497,7 @@
         <v>314</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -9499,7 +9505,7 @@
         <v>314</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -9507,7 +9513,7 @@
         <v>314</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -9515,7 +9521,7 @@
         <v>314</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -9523,7 +9529,7 @@
         <v>314</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -9531,7 +9537,7 @@
         <v>314</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -9539,23 +9545,23 @@
         <v>314</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>314</v>
+        <v>251</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>60</v>
+        <v>253</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>118</v>
+        <v>314</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -9563,7 +9569,7 @@
         <v>315</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>157</v>
+        <v>60</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -9571,7 +9577,7 @@
         <v>315</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -9579,7 +9585,7 @@
         <v>315</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -9587,7 +9593,7 @@
         <v>315</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -9595,7 +9601,7 @@
         <v>315</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -9603,7 +9609,7 @@
         <v>315</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -9611,7 +9617,7 @@
         <v>315</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -9619,23 +9625,23 @@
         <v>315</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>315</v>
+        <v>221</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>85</v>
+        <v>315</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -9643,7 +9649,7 @@
         <v>316</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -9651,7 +9657,7 @@
         <v>316</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -9659,7 +9665,7 @@
         <v>316</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>154</v>
+        <v>93</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -9667,7 +9673,7 @@
         <v>316</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -9675,7 +9681,7 @@
         <v>316</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -9683,7 +9689,7 @@
         <v>316</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -9691,7 +9697,7 @@
         <v>316</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -9699,7 +9705,7 @@
         <v>316</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -9707,7 +9713,7 @@
         <v>316</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -9715,7 +9721,7 @@
         <v>316</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -9723,7 +9729,7 @@
         <v>316</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -9731,7 +9737,7 @@
         <v>316</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -9739,7 +9745,7 @@
         <v>316</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -9747,23 +9753,23 @@
         <v>316</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>316</v>
+        <v>244</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>66</v>
+        <v>302</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>158</v>
+        <v>316</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -9771,7 +9777,7 @@
         <v>318</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -9779,7 +9785,7 @@
         <v>318</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -9787,7 +9793,7 @@
         <v>318</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -9795,7 +9801,7 @@
         <v>318</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>318</v>
+        <v>219</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -9803,13 +9809,29 @@
         <v>318</v>
       </c>
       <c r="B310" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A311" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A312" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B310" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B310">
-    <sortCondition ref="A2:A310"/>
+  <autoFilter ref="A1:B312" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B312">
+    <sortCondition ref="A2:A312"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A48BDAE-6876-4B45-89E4-7280EC32E292}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6813B39-7E16-4CAA-A749-F3C626E66281}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$313</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="348">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1079,6 +1079,9 @@
   </si>
   <si>
     <t>CCIM</t>
+  </si>
+  <si>
+    <t>CGRA</t>
   </si>
 </sst>
 </file>
@@ -1668,10 +1671,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -7270,7 +7269,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:E312"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -8753,15 +8752,15 @@
         <v>310</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>33</v>
+        <v>347</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B179" s="5" t="s">
-        <v>335</v>
+      <c r="B179" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -8769,7 +8768,7 @@
         <v>310</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -8777,7 +8776,7 @@
         <v>310</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -8785,15 +8784,15 @@
         <v>310</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>62</v>
+      <c r="B183" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -8801,7 +8800,7 @@
         <v>310</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -8809,7 +8808,7 @@
         <v>310</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -8817,7 +8816,7 @@
         <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -8825,7 +8824,7 @@
         <v>310</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -8833,7 +8832,7 @@
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -8841,7 +8840,7 @@
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -8849,7 +8848,7 @@
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -8857,7 +8856,7 @@
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -8865,7 +8864,7 @@
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -8873,7 +8872,7 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -8881,7 +8880,7 @@
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -8889,7 +8888,7 @@
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -8897,7 +8896,7 @@
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -8905,7 +8904,7 @@
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -8913,7 +8912,7 @@
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -8921,7 +8920,7 @@
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -8929,7 +8928,7 @@
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -8937,7 +8936,7 @@
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -8945,7 +8944,7 @@
         <v>310</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -8953,7 +8952,7 @@
         <v>310</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -8961,7 +8960,7 @@
         <v>310</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -8969,7 +8968,7 @@
         <v>310</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -8977,7 +8976,7 @@
         <v>310</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -8985,7 +8984,7 @@
         <v>310</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -8993,7 +8992,7 @@
         <v>310</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -9001,7 +9000,7 @@
         <v>310</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -9009,7 +9008,7 @@
         <v>310</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -9017,7 +9016,7 @@
         <v>310</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -9025,7 +9024,7 @@
         <v>310</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -9033,15 +9032,15 @@
         <v>310</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -9049,7 +9048,7 @@
         <v>313</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -9057,7 +9056,7 @@
         <v>313</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -9065,7 +9064,7 @@
         <v>313</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -9073,7 +9072,7 @@
         <v>313</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -9081,7 +9080,7 @@
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -9089,7 +9088,7 @@
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>346</v>
+        <v>46</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -9097,7 +9096,7 @@
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>47</v>
+        <v>346</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -9105,7 +9104,7 @@
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -9113,7 +9112,7 @@
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -9129,7 +9128,7 @@
         <v>313</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -9145,7 +9144,7 @@
         <v>313</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -9153,7 +9152,7 @@
         <v>313</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -9161,7 +9160,7 @@
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -9169,7 +9168,7 @@
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -9177,7 +9176,7 @@
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -9185,7 +9184,7 @@
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -9193,7 +9192,7 @@
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -9201,7 +9200,7 @@
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -9209,7 +9208,7 @@
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -9217,7 +9216,7 @@
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -9225,7 +9224,7 @@
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -9233,7 +9232,7 @@
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -9241,7 +9240,7 @@
         <v>313</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -9249,7 +9248,7 @@
         <v>313</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -9257,7 +9256,7 @@
         <v>313</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -9265,7 +9264,7 @@
         <v>313</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -9273,7 +9272,7 @@
         <v>313</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -9281,7 +9280,7 @@
         <v>313</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -9289,7 +9288,7 @@
         <v>313</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -9297,7 +9296,7 @@
         <v>313</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -9305,7 +9304,7 @@
         <v>313</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -9313,7 +9312,7 @@
         <v>313</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -9321,7 +9320,7 @@
         <v>313</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -9329,7 +9328,7 @@
         <v>313</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>303</v>
+        <v>241</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -9337,15 +9336,15 @@
         <v>313</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -9353,7 +9352,7 @@
         <v>314</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -9361,7 +9360,7 @@
         <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -9369,7 +9368,7 @@
         <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -9377,7 +9376,7 @@
         <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -9385,7 +9384,7 @@
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -9393,7 +9392,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -9401,7 +9400,7 @@
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -9409,7 +9408,7 @@
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -9417,7 +9416,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -9425,7 +9424,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -9433,7 +9432,7 @@
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -9441,7 +9440,7 @@
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -9449,7 +9448,7 @@
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -9457,7 +9456,7 @@
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -9465,7 +9464,7 @@
         <v>314</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -9473,7 +9472,7 @@
         <v>314</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -9481,7 +9480,7 @@
         <v>314</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -9489,7 +9488,7 @@
         <v>314</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -9497,7 +9496,7 @@
         <v>314</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -9505,7 +9504,7 @@
         <v>314</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -9513,7 +9512,7 @@
         <v>314</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -9521,7 +9520,7 @@
         <v>314</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -9529,7 +9528,7 @@
         <v>314</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -9537,7 +9536,7 @@
         <v>314</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -9545,7 +9544,7 @@
         <v>314</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -9553,7 +9552,7 @@
         <v>314</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -9561,15 +9560,15 @@
         <v>314</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>314</v>
+        <v>253</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -9577,7 +9576,7 @@
         <v>315</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -9585,7 +9584,7 @@
         <v>315</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -9593,7 +9592,7 @@
         <v>315</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -9601,7 +9600,7 @@
         <v>315</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -9609,7 +9608,7 @@
         <v>315</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -9617,7 +9616,7 @@
         <v>315</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -9625,7 +9624,7 @@
         <v>315</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -9633,7 +9632,7 @@
         <v>315</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -9641,15 +9640,15 @@
         <v>315</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>315</v>
+        <v>224</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>77</v>
+        <v>315</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -9657,7 +9656,7 @@
         <v>316</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -9665,7 +9664,7 @@
         <v>316</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -9673,7 +9672,7 @@
         <v>316</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -9681,7 +9680,7 @@
         <v>316</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -9689,7 +9688,7 @@
         <v>316</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -9697,7 +9696,7 @@
         <v>316</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -9705,7 +9704,7 @@
         <v>316</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -9713,7 +9712,7 @@
         <v>316</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -9721,7 +9720,7 @@
         <v>316</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -9729,7 +9728,7 @@
         <v>316</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -9737,7 +9736,7 @@
         <v>316</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -9745,7 +9744,7 @@
         <v>316</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -9753,7 +9752,7 @@
         <v>316</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -9761,7 +9760,7 @@
         <v>316</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>302</v>
+        <v>244</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -9769,15 +9768,15 @@
         <v>316</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>66</v>
+        <v>316</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -9785,7 +9784,7 @@
         <v>318</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>158</v>
+        <v>66</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -9793,7 +9792,7 @@
         <v>318</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -9801,7 +9800,7 @@
         <v>318</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -9809,7 +9808,7 @@
         <v>318</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -9817,7 +9816,7 @@
         <v>318</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -9825,13 +9824,21 @@
         <v>318</v>
       </c>
       <c r="B312" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A313" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B312" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B312">
-    <sortCondition ref="A2:A312"/>
+  <autoFilter ref="A1:B313" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B313">
+    <sortCondition ref="A2:A313"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6813B39-7E16-4CAA-A749-F3C626E66281}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9A2E7B3-A7E1-4C9D-82A5-2B06C9BEAC19}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$315</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="350">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1082,6 +1082,12 @@
   </si>
   <si>
     <t>CGRA</t>
+  </si>
+  <si>
+    <t>COAG-VCP</t>
+  </si>
+  <si>
+    <t>GTVC-145</t>
   </si>
 </sst>
 </file>
@@ -7269,7 +7275,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:E315"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -7959,8 +7965,8 @@
       <c r="A79" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>339</v>
+      <c r="B79" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -7968,7 +7974,7 @@
         <v>326</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -7976,7 +7982,7 @@
         <v>326</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -7984,7 +7990,7 @@
         <v>326</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -7992,7 +7998,7 @@
         <v>326</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -8000,7 +8006,7 @@
         <v>326</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -8008,15 +8014,15 @@
         <v>326</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>326</v>
+      <c r="B86" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -8024,7 +8030,7 @@
         <v>326</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>2</v>
+        <v>326</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -8032,7 +8038,7 @@
         <v>326</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>104</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -8040,7 +8046,7 @@
         <v>326</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -8048,7 +8054,7 @@
         <v>326</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -8056,7 +8062,7 @@
         <v>326</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -8064,7 +8070,7 @@
         <v>326</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -8072,7 +8078,7 @@
         <v>326</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -8080,7 +8086,7 @@
         <v>326</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -8088,7 +8094,7 @@
         <v>326</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -8096,7 +8102,7 @@
         <v>326</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -8104,7 +8110,7 @@
         <v>326</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -8112,7 +8118,7 @@
         <v>326</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -8120,7 +8126,7 @@
         <v>326</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -8128,7 +8134,7 @@
         <v>326</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -8136,7 +8142,7 @@
         <v>326</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -8144,7 +8150,7 @@
         <v>326</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -8152,7 +8158,7 @@
         <v>326</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -8160,7 +8166,7 @@
         <v>326</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -8168,7 +8174,7 @@
         <v>326</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -8176,7 +8182,7 @@
         <v>326</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -8184,7 +8190,7 @@
         <v>326</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -8192,7 +8198,7 @@
         <v>326</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
@@ -8200,7 +8206,7 @@
         <v>326</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -8208,7 +8214,7 @@
         <v>326</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -8216,7 +8222,7 @@
         <v>326</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -8224,7 +8230,7 @@
         <v>326</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -8232,7 +8238,7 @@
         <v>326</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -8240,7 +8246,7 @@
         <v>326</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -8248,7 +8254,7 @@
         <v>326</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -8256,7 +8262,7 @@
         <v>326</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -8264,7 +8270,7 @@
         <v>326</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -8272,7 +8278,7 @@
         <v>326</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -8280,7 +8286,7 @@
         <v>326</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -8288,15 +8294,15 @@
         <v>326</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -8304,7 +8310,7 @@
         <v>301</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -8312,7 +8318,7 @@
         <v>301</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -8320,7 +8326,7 @@
         <v>301</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -8328,7 +8334,7 @@
         <v>301</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -8336,7 +8342,7 @@
         <v>301</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -8344,7 +8350,7 @@
         <v>301</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -8352,7 +8358,7 @@
         <v>301</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -8360,7 +8366,7 @@
         <v>301</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -8368,7 +8374,7 @@
         <v>301</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -8376,7 +8382,7 @@
         <v>301</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -8384,7 +8390,7 @@
         <v>301</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -8392,7 +8398,7 @@
         <v>301</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -8400,7 +8406,7 @@
         <v>301</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -8408,7 +8414,7 @@
         <v>301</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -8416,7 +8422,7 @@
         <v>301</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -8424,7 +8430,7 @@
         <v>301</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -8432,7 +8438,7 @@
         <v>301</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -8440,15 +8446,15 @@
         <v>301</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>170</v>
+        <v>301</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -8456,7 +8462,7 @@
         <v>308</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -8464,7 +8470,7 @@
         <v>308</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -8472,7 +8478,7 @@
         <v>308</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -8480,7 +8486,7 @@
         <v>308</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -8488,7 +8494,7 @@
         <v>308</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -8496,7 +8502,7 @@
         <v>308</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -8504,7 +8510,7 @@
         <v>308</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -8512,15 +8518,15 @@
         <v>308</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>4</v>
+        <v>308</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -8528,7 +8534,7 @@
         <v>309</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -8536,7 +8542,7 @@
         <v>309</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -8544,7 +8550,7 @@
         <v>309</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -8552,7 +8558,7 @@
         <v>309</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -8560,7 +8566,7 @@
         <v>309</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -8568,7 +8574,7 @@
         <v>309</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -8576,7 +8582,7 @@
         <v>309</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -8584,7 +8590,7 @@
         <v>309</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -8592,7 +8598,7 @@
         <v>309</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -8600,7 +8606,7 @@
         <v>309</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -8608,7 +8614,7 @@
         <v>309</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -8616,7 +8622,7 @@
         <v>309</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -8624,7 +8630,7 @@
         <v>309</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -8632,7 +8638,7 @@
         <v>309</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -8640,7 +8646,7 @@
         <v>309</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -8648,7 +8654,7 @@
         <v>309</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -8656,7 +8662,7 @@
         <v>309</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -8664,7 +8670,7 @@
         <v>309</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -8672,7 +8678,7 @@
         <v>309</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -8680,7 +8686,7 @@
         <v>309</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -8688,7 +8694,7 @@
         <v>309</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -8696,7 +8702,7 @@
         <v>309</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -8704,7 +8710,7 @@
         <v>309</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -8712,7 +8718,7 @@
         <v>309</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -8720,7 +8726,7 @@
         <v>309</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -8728,7 +8734,7 @@
         <v>309</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -8736,7 +8742,7 @@
         <v>309</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -8744,15 +8750,15 @@
         <v>309</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -8760,15 +8766,15 @@
         <v>310</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>33</v>
+        <v>347</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B180" s="5" t="s">
-        <v>335</v>
+      <c r="B180" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -8776,7 +8782,7 @@
         <v>310</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -8784,7 +8790,7 @@
         <v>310</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -8792,15 +8798,15 @@
         <v>310</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>62</v>
+      <c r="B184" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -8808,7 +8814,7 @@
         <v>310</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -8816,7 +8822,7 @@
         <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -8824,7 +8830,7 @@
         <v>310</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -8832,7 +8838,7 @@
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -8840,7 +8846,7 @@
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -8848,7 +8854,7 @@
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -8856,7 +8862,7 @@
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -8864,7 +8870,7 @@
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -8872,7 +8878,7 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -8880,7 +8886,7 @@
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -8888,7 +8894,7 @@
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -8896,7 +8902,7 @@
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -8904,7 +8910,7 @@
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -8912,7 +8918,7 @@
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -8920,7 +8926,7 @@
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -8928,7 +8934,7 @@
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -8936,7 +8942,7 @@
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -8944,7 +8950,7 @@
         <v>310</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -8952,7 +8958,7 @@
         <v>310</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -8960,7 +8966,7 @@
         <v>310</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -8968,7 +8974,7 @@
         <v>310</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -8976,7 +8982,7 @@
         <v>310</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -8984,7 +8990,7 @@
         <v>310</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -8992,7 +8998,7 @@
         <v>310</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -9000,7 +9006,7 @@
         <v>310</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -9008,7 +9014,7 @@
         <v>310</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -9016,7 +9022,7 @@
         <v>310</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -9024,7 +9030,7 @@
         <v>310</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -9032,7 +9038,7 @@
         <v>310</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -9040,15 +9046,15 @@
         <v>310</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -9056,7 +9062,7 @@
         <v>313</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -9064,7 +9070,7 @@
         <v>313</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -9072,7 +9078,7 @@
         <v>313</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -9080,7 +9086,7 @@
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -9088,7 +9094,7 @@
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -9096,7 +9102,7 @@
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>346</v>
+        <v>46</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -9104,7 +9110,7 @@
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>47</v>
+        <v>346</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -9112,7 +9118,7 @@
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -9120,7 +9126,7 @@
         <v>313</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -9136,7 +9142,7 @@
         <v>313</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -9152,7 +9158,7 @@
         <v>313</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -9160,7 +9166,7 @@
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -9168,7 +9174,7 @@
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -9176,7 +9182,7 @@
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -9184,7 +9190,7 @@
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -9192,7 +9198,7 @@
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -9200,7 +9206,7 @@
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -9208,7 +9214,7 @@
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -9216,7 +9222,7 @@
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -9224,7 +9230,7 @@
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -9232,7 +9238,7 @@
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -9240,7 +9246,7 @@
         <v>313</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -9248,7 +9254,7 @@
         <v>313</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -9256,7 +9262,7 @@
         <v>313</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -9264,7 +9270,7 @@
         <v>313</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -9272,7 +9278,7 @@
         <v>313</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -9280,7 +9286,7 @@
         <v>313</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -9288,7 +9294,7 @@
         <v>313</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -9296,7 +9302,7 @@
         <v>313</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -9304,7 +9310,7 @@
         <v>313</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -9312,7 +9318,7 @@
         <v>313</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -9320,7 +9326,7 @@
         <v>313</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -9328,7 +9334,7 @@
         <v>313</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -9336,7 +9342,7 @@
         <v>313</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>303</v>
+        <v>241</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -9344,15 +9350,15 @@
         <v>313</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -9360,7 +9366,7 @@
         <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>44</v>
+        <v>349</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -9368,7 +9374,7 @@
         <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -9376,7 +9382,7 @@
         <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -9384,7 +9390,7 @@
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -9392,7 +9398,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -9400,7 +9406,7 @@
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -9408,7 +9414,7 @@
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -9416,7 +9422,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -9424,7 +9430,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -9432,7 +9438,7 @@
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -9440,7 +9446,7 @@
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -9448,7 +9454,7 @@
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -9456,7 +9462,7 @@
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -9464,7 +9470,7 @@
         <v>314</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -9472,7 +9478,7 @@
         <v>314</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -9480,7 +9486,7 @@
         <v>314</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -9488,7 +9494,7 @@
         <v>314</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -9496,7 +9502,7 @@
         <v>314</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -9504,7 +9510,7 @@
         <v>314</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -9512,7 +9518,7 @@
         <v>314</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -9520,7 +9526,7 @@
         <v>314</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -9528,7 +9534,7 @@
         <v>314</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -9536,7 +9542,7 @@
         <v>314</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -9544,7 +9550,7 @@
         <v>314</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -9552,7 +9558,7 @@
         <v>314</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -9560,7 +9566,7 @@
         <v>314</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -9568,23 +9574,23 @@
         <v>314</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>314</v>
+        <v>251</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>60</v>
+        <v>253</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>118</v>
+        <v>314</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -9592,7 +9598,7 @@
         <v>315</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>157</v>
+        <v>60</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -9600,7 +9606,7 @@
         <v>315</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -9608,7 +9614,7 @@
         <v>315</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -9616,7 +9622,7 @@
         <v>315</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -9624,7 +9630,7 @@
         <v>315</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -9632,7 +9638,7 @@
         <v>315</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -9640,7 +9646,7 @@
         <v>315</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -9648,23 +9654,23 @@
         <v>315</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>315</v>
+        <v>221</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>85</v>
+        <v>315</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -9672,7 +9678,7 @@
         <v>316</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -9680,7 +9686,7 @@
         <v>316</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -9688,7 +9694,7 @@
         <v>316</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>154</v>
+        <v>93</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -9696,7 +9702,7 @@
         <v>316</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -9704,7 +9710,7 @@
         <v>316</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -9712,7 +9718,7 @@
         <v>316</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -9720,7 +9726,7 @@
         <v>316</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -9728,7 +9734,7 @@
         <v>316</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -9736,7 +9742,7 @@
         <v>316</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -9744,7 +9750,7 @@
         <v>316</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -9752,7 +9758,7 @@
         <v>316</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -9760,7 +9766,7 @@
         <v>316</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -9768,7 +9774,7 @@
         <v>316</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -9776,23 +9782,23 @@
         <v>316</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>316</v>
+        <v>244</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>66</v>
+        <v>302</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>158</v>
+        <v>316</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -9800,7 +9806,7 @@
         <v>318</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -9808,7 +9814,7 @@
         <v>318</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -9816,7 +9822,7 @@
         <v>318</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -9824,7 +9830,7 @@
         <v>318</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>318</v>
+        <v>219</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -9832,13 +9838,29 @@
         <v>318</v>
       </c>
       <c r="B313" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A314" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A315" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B313" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B313">
-    <sortCondition ref="A2:A313"/>
+  <autoFilter ref="A1:B315" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B315">
+    <sortCondition ref="A2:A315"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9A2E7B3-A7E1-4C9D-82A5-2B06C9BEAC19}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A520485-40FC-4A7C-97AC-EDFF8CEDF3B4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$315</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$316</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="351">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1088,6 +1088,9 @@
   </si>
   <si>
     <t>GTVC-145</t>
+  </si>
+  <si>
+    <t>COAG-MAO</t>
   </si>
 </sst>
 </file>
@@ -7275,7 +7278,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:E315"/>
+  <dimension ref="A1:E316"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -7966,15 +7969,15 @@
         <v>326</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>339</v>
+      <c r="B80" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -7982,7 +7985,7 @@
         <v>326</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -7990,7 +7993,7 @@
         <v>326</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -7998,7 +8001,7 @@
         <v>326</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -8006,7 +8009,7 @@
         <v>326</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -8014,7 +8017,7 @@
         <v>326</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -8022,15 +8025,15 @@
         <v>326</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>326</v>
+      <c r="B87" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -8038,7 +8041,7 @@
         <v>326</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>2</v>
+        <v>326</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -8046,7 +8049,7 @@
         <v>326</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>104</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -8054,7 +8057,7 @@
         <v>326</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -8062,7 +8065,7 @@
         <v>326</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -8070,7 +8073,7 @@
         <v>326</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -8078,7 +8081,7 @@
         <v>326</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -8086,7 +8089,7 @@
         <v>326</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -8094,7 +8097,7 @@
         <v>326</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -8102,7 +8105,7 @@
         <v>326</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -8110,7 +8113,7 @@
         <v>326</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -8118,7 +8121,7 @@
         <v>326</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -8126,7 +8129,7 @@
         <v>326</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -8134,7 +8137,7 @@
         <v>326</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -8142,7 +8145,7 @@
         <v>326</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -8150,7 +8153,7 @@
         <v>326</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -8158,7 +8161,7 @@
         <v>326</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -8166,7 +8169,7 @@
         <v>326</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -8174,7 +8177,7 @@
         <v>326</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -8182,7 +8185,7 @@
         <v>326</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -8190,7 +8193,7 @@
         <v>326</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -8198,7 +8201,7 @@
         <v>326</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
@@ -8206,7 +8209,7 @@
         <v>326</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -8214,7 +8217,7 @@
         <v>326</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -8222,7 +8225,7 @@
         <v>326</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -8230,7 +8233,7 @@
         <v>326</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -8238,7 +8241,7 @@
         <v>326</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -8246,7 +8249,7 @@
         <v>326</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -8254,7 +8257,7 @@
         <v>326</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -8262,7 +8265,7 @@
         <v>326</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -8270,7 +8273,7 @@
         <v>326</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -8278,7 +8281,7 @@
         <v>326</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -8286,7 +8289,7 @@
         <v>326</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -8294,7 +8297,7 @@
         <v>326</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -8302,15 +8305,15 @@
         <v>326</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -8318,7 +8321,7 @@
         <v>301</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -8326,7 +8329,7 @@
         <v>301</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -8334,7 +8337,7 @@
         <v>301</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -8342,7 +8345,7 @@
         <v>301</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -8350,7 +8353,7 @@
         <v>301</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -8358,7 +8361,7 @@
         <v>301</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -8366,7 +8369,7 @@
         <v>301</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -8374,7 +8377,7 @@
         <v>301</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -8382,7 +8385,7 @@
         <v>301</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -8390,7 +8393,7 @@
         <v>301</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -8398,7 +8401,7 @@
         <v>301</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -8406,7 +8409,7 @@
         <v>301</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -8414,7 +8417,7 @@
         <v>301</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -8422,7 +8425,7 @@
         <v>301</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -8430,7 +8433,7 @@
         <v>301</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -8438,7 +8441,7 @@
         <v>301</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -8446,7 +8449,7 @@
         <v>301</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -8454,15 +8457,15 @@
         <v>301</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>170</v>
+        <v>301</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -8470,7 +8473,7 @@
         <v>308</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -8478,7 +8481,7 @@
         <v>308</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -8486,7 +8489,7 @@
         <v>308</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -8494,7 +8497,7 @@
         <v>308</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -8502,7 +8505,7 @@
         <v>308</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -8510,7 +8513,7 @@
         <v>308</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -8518,7 +8521,7 @@
         <v>308</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -8526,15 +8529,15 @@
         <v>308</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>4</v>
+        <v>308</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -8542,7 +8545,7 @@
         <v>309</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -8550,7 +8553,7 @@
         <v>309</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -8558,7 +8561,7 @@
         <v>309</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -8566,7 +8569,7 @@
         <v>309</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -8574,7 +8577,7 @@
         <v>309</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -8582,7 +8585,7 @@
         <v>309</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -8590,7 +8593,7 @@
         <v>309</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -8598,7 +8601,7 @@
         <v>309</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -8606,7 +8609,7 @@
         <v>309</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -8614,7 +8617,7 @@
         <v>309</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -8622,7 +8625,7 @@
         <v>309</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -8630,7 +8633,7 @@
         <v>309</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -8638,7 +8641,7 @@
         <v>309</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -8646,7 +8649,7 @@
         <v>309</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -8654,7 +8657,7 @@
         <v>309</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -8662,7 +8665,7 @@
         <v>309</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -8670,7 +8673,7 @@
         <v>309</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -8678,7 +8681,7 @@
         <v>309</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -8686,7 +8689,7 @@
         <v>309</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -8694,7 +8697,7 @@
         <v>309</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -8702,7 +8705,7 @@
         <v>309</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -8710,7 +8713,7 @@
         <v>309</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -8718,7 +8721,7 @@
         <v>309</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -8726,7 +8729,7 @@
         <v>309</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -8734,7 +8737,7 @@
         <v>309</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -8742,7 +8745,7 @@
         <v>309</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -8750,7 +8753,7 @@
         <v>309</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -8758,15 +8761,15 @@
         <v>309</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -8774,15 +8777,15 @@
         <v>310</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>33</v>
+        <v>347</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B181" s="5" t="s">
-        <v>335</v>
+      <c r="B181" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -8790,7 +8793,7 @@
         <v>310</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -8798,7 +8801,7 @@
         <v>310</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -8806,15 +8809,15 @@
         <v>310</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>62</v>
+      <c r="B185" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -8822,7 +8825,7 @@
         <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -8830,7 +8833,7 @@
         <v>310</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -8838,7 +8841,7 @@
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -8846,7 +8849,7 @@
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -8854,7 +8857,7 @@
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -8862,7 +8865,7 @@
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -8870,7 +8873,7 @@
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -8878,7 +8881,7 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -8886,7 +8889,7 @@
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -8894,7 +8897,7 @@
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -8902,7 +8905,7 @@
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -8910,7 +8913,7 @@
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -8918,7 +8921,7 @@
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -8926,7 +8929,7 @@
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -8934,7 +8937,7 @@
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -8942,7 +8945,7 @@
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -8950,7 +8953,7 @@
         <v>310</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -8958,7 +8961,7 @@
         <v>310</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -8966,7 +8969,7 @@
         <v>310</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -8974,7 +8977,7 @@
         <v>310</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -8982,7 +8985,7 @@
         <v>310</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -8990,7 +8993,7 @@
         <v>310</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -8998,7 +9001,7 @@
         <v>310</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -9006,7 +9009,7 @@
         <v>310</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -9014,7 +9017,7 @@
         <v>310</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -9022,7 +9025,7 @@
         <v>310</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -9030,7 +9033,7 @@
         <v>310</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -9038,7 +9041,7 @@
         <v>310</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -9046,7 +9049,7 @@
         <v>310</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -9054,15 +9057,15 @@
         <v>310</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -9070,7 +9073,7 @@
         <v>313</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -9078,7 +9081,7 @@
         <v>313</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -9086,7 +9089,7 @@
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -9094,7 +9097,7 @@
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -9102,7 +9105,7 @@
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -9110,7 +9113,7 @@
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>346</v>
+        <v>46</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -9118,7 +9121,7 @@
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>47</v>
+        <v>346</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -9126,7 +9129,7 @@
         <v>313</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -9134,7 +9137,7 @@
         <v>313</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -9150,7 +9153,7 @@
         <v>313</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -9166,7 +9169,7 @@
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -9174,7 +9177,7 @@
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -9182,7 +9185,7 @@
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -9190,7 +9193,7 @@
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -9198,7 +9201,7 @@
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -9206,7 +9209,7 @@
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -9214,7 +9217,7 @@
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -9222,7 +9225,7 @@
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -9230,7 +9233,7 @@
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -9238,7 +9241,7 @@
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -9246,7 +9249,7 @@
         <v>313</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -9254,7 +9257,7 @@
         <v>313</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -9262,7 +9265,7 @@
         <v>313</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -9270,7 +9273,7 @@
         <v>313</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -9278,7 +9281,7 @@
         <v>313</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -9286,7 +9289,7 @@
         <v>313</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -9294,7 +9297,7 @@
         <v>313</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -9302,7 +9305,7 @@
         <v>313</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -9310,7 +9313,7 @@
         <v>313</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -9318,7 +9321,7 @@
         <v>313</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -9326,7 +9329,7 @@
         <v>313</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -9334,7 +9337,7 @@
         <v>313</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -9342,7 +9345,7 @@
         <v>313</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -9350,7 +9353,7 @@
         <v>313</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>303</v>
+        <v>241</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -9358,15 +9361,15 @@
         <v>313</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>349</v>
+        <v>313</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -9374,7 +9377,7 @@
         <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>21</v>
+        <v>349</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -9382,7 +9385,7 @@
         <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -9390,7 +9393,7 @@
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -9398,7 +9401,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -9406,7 +9409,7 @@
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -9414,7 +9417,7 @@
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -9422,7 +9425,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -9430,7 +9433,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -9438,7 +9441,7 @@
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -9446,7 +9449,7 @@
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -9454,7 +9457,7 @@
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -9462,7 +9465,7 @@
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -9470,7 +9473,7 @@
         <v>314</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -9478,7 +9481,7 @@
         <v>314</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -9486,7 +9489,7 @@
         <v>314</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -9494,7 +9497,7 @@
         <v>314</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -9502,7 +9505,7 @@
         <v>314</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -9510,7 +9513,7 @@
         <v>314</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -9518,7 +9521,7 @@
         <v>314</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -9526,7 +9529,7 @@
         <v>314</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -9534,7 +9537,7 @@
         <v>314</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -9542,7 +9545,7 @@
         <v>314</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -9550,7 +9553,7 @@
         <v>314</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -9558,7 +9561,7 @@
         <v>314</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -9566,7 +9569,7 @@
         <v>314</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -9574,7 +9577,7 @@
         <v>314</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -9582,7 +9585,7 @@
         <v>314</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -9590,15 +9593,15 @@
         <v>314</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>314</v>
+        <v>253</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -9606,7 +9609,7 @@
         <v>315</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -9614,7 +9617,7 @@
         <v>315</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -9622,7 +9625,7 @@
         <v>315</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -9630,7 +9633,7 @@
         <v>315</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -9638,7 +9641,7 @@
         <v>315</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -9646,7 +9649,7 @@
         <v>315</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -9654,7 +9657,7 @@
         <v>315</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -9662,7 +9665,7 @@
         <v>315</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -9670,15 +9673,15 @@
         <v>315</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>315</v>
+        <v>224</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>77</v>
+        <v>315</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -9686,7 +9689,7 @@
         <v>316</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -9694,7 +9697,7 @@
         <v>316</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -9702,7 +9705,7 @@
         <v>316</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -9710,7 +9713,7 @@
         <v>316</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -9718,7 +9721,7 @@
         <v>316</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -9726,7 +9729,7 @@
         <v>316</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -9734,7 +9737,7 @@
         <v>316</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -9742,7 +9745,7 @@
         <v>316</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -9750,7 +9753,7 @@
         <v>316</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -9758,7 +9761,7 @@
         <v>316</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -9766,7 +9769,7 @@
         <v>316</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -9774,7 +9777,7 @@
         <v>316</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -9782,7 +9785,7 @@
         <v>316</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -9790,7 +9793,7 @@
         <v>316</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>302</v>
+        <v>244</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -9798,15 +9801,15 @@
         <v>316</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>66</v>
+        <v>316</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -9814,7 +9817,7 @@
         <v>318</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>158</v>
+        <v>66</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -9822,7 +9825,7 @@
         <v>318</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -9830,7 +9833,7 @@
         <v>318</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -9838,7 +9841,7 @@
         <v>318</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -9846,7 +9849,7 @@
         <v>318</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -9854,13 +9857,21 @@
         <v>318</v>
       </c>
       <c r="B315" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A316" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B315" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B315">
-    <sortCondition ref="A2:A315"/>
+  <autoFilter ref="A1:B316" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B316">
+    <sortCondition ref="A2:A316"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A520485-40FC-4A7C-97AC-EDFF8CEDF3B4}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6F89108-B0F5-4FE5-B997-C9CAB090C763}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$318</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="353">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1091,6 +1091,12 @@
   </si>
   <si>
     <t>COAG-MAO</t>
+  </si>
+  <si>
+    <t>GTEC</t>
+  </si>
+  <si>
+    <t>CPEA</t>
   </si>
 </sst>
 </file>
@@ -7278,7 +7284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -7313,9 +7319,9 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -7323,7 +7329,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="1"/>
@@ -7333,9 +7339,9 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -7343,17 +7349,17 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>235</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -7363,9 +7369,9 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -7373,17 +7379,17 @@
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -7393,7 +7399,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -7403,27 +7409,27 @@
         <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -7433,17 +7439,17 @@
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="1"/>
@@ -7453,7 +7459,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="1"/>
@@ -7463,7 +7469,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="1"/>
@@ -7473,9 +7479,9 @@
         <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="D19" s="2"/>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -7483,9 +7489,9 @@
         <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -7493,9 +7499,9 @@
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="D21" s="2"/>
       <c r="E21" s="1"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -7503,7 +7509,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -7513,9 +7519,9 @@
         <v>26</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -7523,9 +7529,9 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -7533,7 +7539,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -7543,7 +7549,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -7553,15 +7559,17 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>292</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -7569,15 +7577,15 @@
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>333</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -7585,7 +7593,7 @@
         <v>333</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -7593,15 +7601,15 @@
         <v>333</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
@@ -7609,7 +7617,7 @@
         <v>334</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
@@ -7617,7 +7625,7 @@
         <v>334</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
@@ -7625,39 +7633,39 @@
         <v>334</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>330</v>
+        <v>143</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>280</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -7665,7 +7673,7 @@
         <v>330</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -7673,7 +7681,7 @@
         <v>330</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
@@ -7681,23 +7689,23 @@
         <v>330</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>35</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
@@ -7705,7 +7713,7 @@
         <v>300</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
@@ -7713,7 +7721,7 @@
         <v>300</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
@@ -7721,7 +7729,7 @@
         <v>300</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
@@ -7729,7 +7737,7 @@
         <v>300</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -7737,7 +7745,7 @@
         <v>300</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
@@ -7745,7 +7753,7 @@
         <v>300</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
@@ -7753,7 +7761,7 @@
         <v>300</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -7761,7 +7769,7 @@
         <v>300</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -7769,7 +7777,7 @@
         <v>300</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
@@ -7777,7 +7785,7 @@
         <v>300</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
@@ -7785,7 +7793,7 @@
         <v>300</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
@@ -7793,7 +7801,7 @@
         <v>300</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
@@ -7801,7 +7809,7 @@
         <v>300</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -7809,7 +7817,7 @@
         <v>300</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -7817,7 +7825,7 @@
         <v>300</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -7825,7 +7833,7 @@
         <v>300</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
@@ -7833,7 +7841,7 @@
         <v>300</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
@@ -7841,7 +7849,7 @@
         <v>300</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
@@ -7849,7 +7857,7 @@
         <v>300</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -7857,7 +7865,7 @@
         <v>300</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
@@ -7865,7 +7873,7 @@
         <v>300</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -7873,7 +7881,7 @@
         <v>300</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
@@ -7881,7 +7889,7 @@
         <v>300</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
@@ -7889,7 +7897,7 @@
         <v>300</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -7897,7 +7905,7 @@
         <v>300</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -7905,7 +7913,7 @@
         <v>300</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
@@ -7913,7 +7921,7 @@
         <v>300</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -7921,7 +7929,7 @@
         <v>300</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -7929,7 +7937,7 @@
         <v>300</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
@@ -7937,7 +7945,7 @@
         <v>300</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -7945,7 +7953,7 @@
         <v>300</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -7953,7 +7961,7 @@
         <v>300</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -7961,15 +7969,15 @@
         <v>300</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -7977,15 +7985,15 @@
         <v>326</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>339</v>
+      <c r="B81" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -7993,7 +8001,7 @@
         <v>326</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -8001,7 +8009,7 @@
         <v>326</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -8009,7 +8017,7 @@
         <v>326</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -8017,7 +8025,7 @@
         <v>326</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -8025,7 +8033,7 @@
         <v>326</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -8033,15 +8041,15 @@
         <v>326</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>326</v>
+      <c r="B88" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -8049,7 +8057,7 @@
         <v>326</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>2</v>
+        <v>326</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -8057,7 +8065,7 @@
         <v>326</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>104</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -8065,7 +8073,7 @@
         <v>326</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -8073,7 +8081,7 @@
         <v>326</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -8081,7 +8089,7 @@
         <v>326</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -8089,7 +8097,7 @@
         <v>326</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -8097,7 +8105,7 @@
         <v>326</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -8105,7 +8113,7 @@
         <v>326</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -8113,7 +8121,7 @@
         <v>326</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -8121,7 +8129,7 @@
         <v>326</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -8129,7 +8137,7 @@
         <v>326</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -8137,7 +8145,7 @@
         <v>326</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -8145,7 +8153,7 @@
         <v>326</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -8153,7 +8161,7 @@
         <v>326</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -8161,7 +8169,7 @@
         <v>326</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -8169,7 +8177,7 @@
         <v>326</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -8177,7 +8185,7 @@
         <v>326</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -8185,7 +8193,7 @@
         <v>326</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -8193,7 +8201,7 @@
         <v>326</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -8201,7 +8209,7 @@
         <v>326</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
@@ -8209,7 +8217,7 @@
         <v>326</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -8217,7 +8225,7 @@
         <v>326</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -8225,7 +8233,7 @@
         <v>326</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -8233,7 +8241,7 @@
         <v>326</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -8241,7 +8249,7 @@
         <v>326</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -8249,7 +8257,7 @@
         <v>326</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -8257,7 +8265,7 @@
         <v>326</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -8265,7 +8273,7 @@
         <v>326</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -8273,7 +8281,7 @@
         <v>326</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -8281,7 +8289,7 @@
         <v>326</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -8289,7 +8297,7 @@
         <v>326</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -8297,7 +8305,7 @@
         <v>326</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -8305,7 +8313,7 @@
         <v>326</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -8313,15 +8321,15 @@
         <v>326</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -8329,7 +8337,7 @@
         <v>301</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -8337,7 +8345,7 @@
         <v>301</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -8345,7 +8353,7 @@
         <v>301</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -8353,7 +8361,7 @@
         <v>301</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -8361,7 +8369,7 @@
         <v>301</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -8369,7 +8377,7 @@
         <v>301</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -8377,7 +8385,7 @@
         <v>301</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -8385,7 +8393,7 @@
         <v>301</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -8393,7 +8401,7 @@
         <v>301</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -8401,7 +8409,7 @@
         <v>301</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -8409,7 +8417,7 @@
         <v>301</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -8417,7 +8425,7 @@
         <v>301</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -8425,7 +8433,7 @@
         <v>301</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -8433,7 +8441,7 @@
         <v>301</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -8441,7 +8449,7 @@
         <v>301</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -8449,7 +8457,7 @@
         <v>301</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -8457,7 +8465,7 @@
         <v>301</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -8465,15 +8473,15 @@
         <v>301</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>170</v>
+        <v>301</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -8481,7 +8489,7 @@
         <v>308</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -8489,7 +8497,7 @@
         <v>308</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -8497,7 +8505,7 @@
         <v>308</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -8505,7 +8513,7 @@
         <v>308</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -8513,7 +8521,7 @@
         <v>308</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -8521,7 +8529,7 @@
         <v>308</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -8529,7 +8537,7 @@
         <v>308</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -8537,15 +8545,15 @@
         <v>308</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>4</v>
+        <v>308</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -8553,7 +8561,7 @@
         <v>309</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -8561,7 +8569,7 @@
         <v>309</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -8569,7 +8577,7 @@
         <v>309</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -8577,7 +8585,7 @@
         <v>309</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -8585,7 +8593,7 @@
         <v>309</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -8593,7 +8601,7 @@
         <v>309</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -8601,7 +8609,7 @@
         <v>309</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -8609,7 +8617,7 @@
         <v>309</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -8617,7 +8625,7 @@
         <v>309</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -8625,7 +8633,7 @@
         <v>309</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -8633,7 +8641,7 @@
         <v>309</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -8641,7 +8649,7 @@
         <v>309</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -8649,7 +8657,7 @@
         <v>309</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -8657,7 +8665,7 @@
         <v>309</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -8665,7 +8673,7 @@
         <v>309</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -8673,7 +8681,7 @@
         <v>309</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -8681,7 +8689,7 @@
         <v>309</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -8689,7 +8697,7 @@
         <v>309</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -8697,7 +8705,7 @@
         <v>309</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -8705,7 +8713,7 @@
         <v>309</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -8713,7 +8721,7 @@
         <v>309</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -8721,7 +8729,7 @@
         <v>309</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -8729,7 +8737,7 @@
         <v>309</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -8737,7 +8745,7 @@
         <v>309</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -8745,7 +8753,7 @@
         <v>309</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -8753,7 +8761,7 @@
         <v>309</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -8761,7 +8769,7 @@
         <v>309</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -8769,15 +8777,15 @@
         <v>309</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -8785,23 +8793,23 @@
         <v>310</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B182" s="5" t="s">
-        <v>335</v>
+      <c r="B182" s="2" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B183" s="5" t="s">
-        <v>336</v>
+      <c r="B183" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -8809,7 +8817,7 @@
         <v>310</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -8817,23 +8825,23 @@
         <v>310</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>62</v>
+      <c r="B186" s="5" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>86</v>
+      <c r="B187" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -8841,7 +8849,7 @@
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -8849,7 +8857,7 @@
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -8857,7 +8865,7 @@
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -8865,7 +8873,7 @@
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -8873,7 +8881,7 @@
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -8881,7 +8889,7 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -8889,7 +8897,7 @@
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -8897,7 +8905,7 @@
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -8905,7 +8913,7 @@
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -8913,7 +8921,7 @@
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -8921,7 +8929,7 @@
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -8929,7 +8937,7 @@
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -8937,7 +8945,7 @@
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -8945,7 +8953,7 @@
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -8953,7 +8961,7 @@
         <v>310</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -8961,7 +8969,7 @@
         <v>310</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -8969,7 +8977,7 @@
         <v>310</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -8977,7 +8985,7 @@
         <v>310</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -8985,7 +8993,7 @@
         <v>310</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -8993,7 +9001,7 @@
         <v>310</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -9001,7 +9009,7 @@
         <v>310</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -9009,7 +9017,7 @@
         <v>310</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -9017,7 +9025,7 @@
         <v>310</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -9025,7 +9033,7 @@
         <v>310</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -9033,7 +9041,7 @@
         <v>310</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -9041,7 +9049,7 @@
         <v>310</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>287</v>
+        <v>236</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -9049,7 +9057,7 @@
         <v>310</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -9057,7 +9065,7 @@
         <v>310</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -9065,23 +9073,23 @@
         <v>310</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>29</v>
+        <v>310</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>37</v>
+        <v>320</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -9089,7 +9097,7 @@
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -9097,7 +9105,7 @@
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -9105,7 +9113,7 @@
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -9113,7 +9121,7 @@
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -9121,7 +9129,7 @@
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>346</v>
+        <v>45</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -9129,7 +9137,7 @@
         <v>313</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -9137,7 +9145,7 @@
         <v>313</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>52</v>
+        <v>346</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -9145,7 +9153,7 @@
         <v>313</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -9153,7 +9161,7 @@
         <v>313</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -9161,7 +9169,7 @@
         <v>313</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -9169,7 +9177,7 @@
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -9177,7 +9185,7 @@
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -9185,7 +9193,7 @@
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -9193,7 +9201,7 @@
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -9201,7 +9209,7 @@
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -9209,7 +9217,7 @@
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -9217,7 +9225,7 @@
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -9225,7 +9233,7 @@
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -9233,7 +9241,7 @@
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -9241,7 +9249,7 @@
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -9249,7 +9257,7 @@
         <v>313</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -9257,7 +9265,7 @@
         <v>313</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -9265,7 +9273,7 @@
         <v>313</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -9273,7 +9281,7 @@
         <v>313</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -9281,7 +9289,7 @@
         <v>313</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -9289,7 +9297,7 @@
         <v>313</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -9297,7 +9305,7 @@
         <v>313</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -9305,7 +9313,7 @@
         <v>313</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -9313,7 +9321,7 @@
         <v>313</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -9321,7 +9329,7 @@
         <v>313</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -9329,7 +9337,7 @@
         <v>313</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -9337,7 +9345,7 @@
         <v>313</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -9345,7 +9353,7 @@
         <v>313</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -9353,7 +9361,7 @@
         <v>313</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -9361,7 +9369,7 @@
         <v>313</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>303</v>
+        <v>230</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -9369,23 +9377,23 @@
         <v>313</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>313</v>
+        <v>241</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>349</v>
+        <v>303</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -9393,7 +9401,7 @@
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>44</v>
+        <v>349</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -9401,7 +9409,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -9409,7 +9417,7 @@
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -9417,7 +9425,7 @@
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -9425,7 +9433,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -9433,7 +9441,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -9441,7 +9449,7 @@
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -9449,7 +9457,7 @@
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -9457,7 +9465,7 @@
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -9465,7 +9473,7 @@
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -9473,7 +9481,7 @@
         <v>314</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -9481,7 +9489,7 @@
         <v>314</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -9489,7 +9497,7 @@
         <v>314</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -9497,7 +9505,7 @@
         <v>314</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -9505,7 +9513,7 @@
         <v>314</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -9513,7 +9521,7 @@
         <v>314</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -9521,7 +9529,7 @@
         <v>314</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -9529,7 +9537,7 @@
         <v>314</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -9537,7 +9545,7 @@
         <v>314</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -9545,7 +9553,7 @@
         <v>314</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -9553,7 +9561,7 @@
         <v>314</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -9561,7 +9569,7 @@
         <v>314</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -9569,7 +9577,7 @@
         <v>314</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -9577,7 +9585,7 @@
         <v>314</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -9585,7 +9593,7 @@
         <v>314</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -9593,7 +9601,7 @@
         <v>314</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -9601,23 +9609,23 @@
         <v>314</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>314</v>
+        <v>251</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>60</v>
+        <v>253</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>118</v>
+        <v>314</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -9625,7 +9633,7 @@
         <v>315</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>157</v>
+        <v>60</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -9633,7 +9641,7 @@
         <v>315</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -9641,7 +9649,7 @@
         <v>315</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -9649,7 +9657,7 @@
         <v>315</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -9657,7 +9665,7 @@
         <v>315</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -9665,7 +9673,7 @@
         <v>315</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -9673,7 +9681,7 @@
         <v>315</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -9681,23 +9689,23 @@
         <v>315</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>315</v>
+        <v>221</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>85</v>
+        <v>315</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -9705,7 +9713,7 @@
         <v>316</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -9713,7 +9721,7 @@
         <v>316</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -9721,7 +9729,7 @@
         <v>316</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>154</v>
+        <v>93</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -9729,7 +9737,7 @@
         <v>316</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -9737,7 +9745,7 @@
         <v>316</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -9745,7 +9753,7 @@
         <v>316</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -9753,7 +9761,7 @@
         <v>316</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -9761,7 +9769,7 @@
         <v>316</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -9769,7 +9777,7 @@
         <v>316</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -9777,7 +9785,7 @@
         <v>316</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -9785,7 +9793,7 @@
         <v>316</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -9793,7 +9801,7 @@
         <v>316</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -9801,7 +9809,7 @@
         <v>316</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -9809,23 +9817,23 @@
         <v>316</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>316</v>
+        <v>244</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>66</v>
+        <v>302</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>158</v>
+        <v>316</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -9833,7 +9841,7 @@
         <v>318</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -9841,7 +9849,7 @@
         <v>318</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -9849,7 +9857,7 @@
         <v>318</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -9857,7 +9865,7 @@
         <v>318</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>318</v>
+        <v>219</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
@@ -9865,13 +9873,29 @@
         <v>318</v>
       </c>
       <c r="B316" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A317" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A318" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B316" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B316">
-    <sortCondition ref="A2:A316"/>
+  <autoFilter ref="A1:B318" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B318">
+    <sortCondition ref="A2:A318"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
